--- a/artfynd/A 38113-2024 artfynd.xlsx
+++ b/artfynd/A 38113-2024 artfynd.xlsx
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120399383</v>
+        <v>120400005</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565821</v>
+        <v>565902</v>
       </c>
       <c r="R16" t="n">
-        <v>7041341</v>
+        <v>7041379</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,7 +2433,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400005</v>
+        <v>120399679</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2468,12 +2468,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2482,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565902</v>
+        <v>565831</v>
       </c>
       <c r="R17" t="n">
-        <v>7041379</v>
+        <v>7041314</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2517,7 +2512,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2527,7 +2522,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,19 +2537,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120399679</v>
+        <v>120399383</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2589,7 +2584,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565831</v>
+        <v>565821</v>
       </c>
       <c r="R18" t="n">
-        <v>7041314</v>
+        <v>7041341</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,12 +2658,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120399901</v>
+        <v>120399022</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2942,7 +2942,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2951,10 +2956,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565882</v>
+        <v>565878</v>
       </c>
       <c r="R21" t="n">
-        <v>7041329</v>
+        <v>7041450</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2991,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2996,7 +3001,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,19 +3016,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120399022</v>
+        <v>120399901</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3058,12 +3063,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565878</v>
+        <v>565882</v>
       </c>
       <c r="R22" t="n">
-        <v>7041450</v>
+        <v>7041329</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3132,12 +3132,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 38113-2024 artfynd.xlsx
+++ b/artfynd/A 38113-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120400132</v>
+        <v>120400192</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565913</v>
+        <v>565904</v>
       </c>
       <c r="R2" t="n">
-        <v>7041387</v>
+        <v>7041409</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120400192</v>
+        <v>120400199</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565904</v>
+        <v>565908</v>
       </c>
       <c r="R3" t="n">
-        <v>7041409</v>
+        <v>7041415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120398886</v>
+        <v>120399901</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +915,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565779</v>
+        <v>565882</v>
       </c>
       <c r="R4" t="n">
-        <v>7041539</v>
+        <v>7041329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1132,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120398926</v>
+        <v>120398741</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,35 +1143,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565839</v>
+        <v>565735</v>
       </c>
       <c r="R6" t="n">
-        <v>7041485</v>
+        <v>7041597</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,19 +1240,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120399057</v>
+        <v>120399383</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1288,7 +1287,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565825</v>
+        <v>565821</v>
       </c>
       <c r="R7" t="n">
-        <v>7041411</v>
+        <v>7041341</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,22 +1361,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120399714</v>
+        <v>120398886</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,47 +1385,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565824</v>
+        <v>565779</v>
       </c>
       <c r="R8" t="n">
-        <v>7041328</v>
+        <v>7041539</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1448,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1458,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,22 +1473,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120398741</v>
+        <v>120399818</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,35 +1497,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1539,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565735</v>
+        <v>565848</v>
       </c>
       <c r="R9" t="n">
-        <v>7041597</v>
+        <v>7041334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,22 +1594,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120400199</v>
+        <v>120400275</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,42 +1618,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565908</v>
+        <v>565901</v>
       </c>
       <c r="R10" t="n">
-        <v>7041415</v>
+        <v>7041422</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120399818</v>
+        <v>120399352</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,47 +1730,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565848</v>
+        <v>565772</v>
       </c>
       <c r="R11" t="n">
-        <v>7041334</v>
+        <v>7041373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,19 +1818,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120399580</v>
+        <v>120400312</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1883,7 +1865,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1892,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565788</v>
+        <v>565899</v>
       </c>
       <c r="R12" t="n">
-        <v>7041338</v>
+        <v>7041429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,7 +1946,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400105</v>
+        <v>120398926</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1999,7 +1981,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2008,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565897</v>
+        <v>565839</v>
       </c>
       <c r="R13" t="n">
-        <v>7041392</v>
+        <v>7041485</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2053,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,19 +2055,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120399881</v>
+        <v>120399746</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2115,7 +2102,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2124,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565862</v>
+        <v>565852</v>
       </c>
       <c r="R14" t="n">
-        <v>7041347</v>
+        <v>7041322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398916</v>
+        <v>120399057</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2240,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565812</v>
+        <v>565825</v>
       </c>
       <c r="R15" t="n">
-        <v>7041489</v>
+        <v>7041411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2275,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2285,7 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,7 +2299,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120400005</v>
+        <v>120400333</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2347,7 +2334,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2361,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565902</v>
+        <v>565841</v>
       </c>
       <c r="R16" t="n">
-        <v>7041379</v>
+        <v>7041478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120399679</v>
+        <v>120399714</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2468,7 +2455,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2477,10 +2469,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565831</v>
+        <v>565824</v>
       </c>
       <c r="R17" t="n">
-        <v>7041314</v>
+        <v>7041328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2512,7 +2504,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2522,7 +2514,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,19 +2529,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120399383</v>
+        <v>120399580</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2584,12 +2576,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2598,10 +2585,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565821</v>
+        <v>565788</v>
       </c>
       <c r="R18" t="n">
-        <v>7041341</v>
+        <v>7041338</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2633,7 +2620,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2643,7 +2630,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,19 +2645,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120399614</v>
+        <v>120399968</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2708,21 +2695,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565824</v>
+        <v>565894</v>
       </c>
       <c r="R19" t="n">
-        <v>7041305</v>
+        <v>7041345</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2754,7 +2736,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2746,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,19 +2761,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120399994</v>
+        <v>120399022</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2826,7 +2808,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2835,10 +2822,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565902</v>
+        <v>565878</v>
       </c>
       <c r="R20" t="n">
-        <v>7041372</v>
+        <v>7041450</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2870,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2880,7 +2867,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2895,19 +2882,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120399022</v>
+        <v>120398916</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2942,12 +2929,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2956,10 +2938,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565878</v>
+        <v>565812</v>
       </c>
       <c r="R21" t="n">
-        <v>7041450</v>
+        <v>7041489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,7 +2973,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3001,7 +2983,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3016,19 +2998,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120399901</v>
+        <v>120400005</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3063,7 +3045,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3072,10 +3059,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565882</v>
+        <v>565902</v>
       </c>
       <c r="R22" t="n">
-        <v>7041329</v>
+        <v>7041379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3094,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,7 +3104,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3132,22 +3119,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120400275</v>
+        <v>120399881</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,38 +3143,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565901</v>
+        <v>565862</v>
       </c>
       <c r="R23" t="n">
-        <v>7041422</v>
+        <v>7041347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3219,7 +3210,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3229,7 +3220,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3256,10 +3247,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120400024</v>
+        <v>120399614</v>
       </c>
       <c r="B24" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,36 +3259,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3306,13 +3296,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565892</v>
+        <v>565824</v>
       </c>
       <c r="R24" t="n">
-        <v>7041371</v>
+        <v>7041305</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3341,7 +3331,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3351,7 +3341,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3378,7 +3368,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400312</v>
+        <v>120399679</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3413,7 +3403,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3422,10 +3412,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565899</v>
+        <v>565831</v>
       </c>
       <c r="R25" t="n">
-        <v>7041429</v>
+        <v>7041314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3457,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3467,7 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3494,7 +3484,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120399428</v>
+        <v>120399994</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3529,12 +3519,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3543,10 +3528,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565805</v>
+        <v>565902</v>
       </c>
       <c r="R26" t="n">
-        <v>7041355</v>
+        <v>7041372</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,7 +3563,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3588,7 +3573,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3603,22 +3588,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120399352</v>
+        <v>120399428</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3627,38 +3612,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565772</v>
+        <v>565805</v>
       </c>
       <c r="R27" t="n">
-        <v>7041373</v>
+        <v>7041355</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3690,7 +3684,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3700,7 +3694,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3715,22 +3709,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120399968</v>
+        <v>120400024</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3739,30 +3733,36 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565894</v>
+        <v>565892</v>
       </c>
       <c r="R28" t="n">
-        <v>7041345</v>
+        <v>7041371</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3831,19 +3831,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120399746</v>
+        <v>120400105</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565852</v>
+        <v>565897</v>
       </c>
       <c r="R29" t="n">
-        <v>7041322</v>
+        <v>7041392</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3959,7 +3959,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400333</v>
+        <v>120400132</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565841</v>
+        <v>565913</v>
       </c>
       <c r="R30" t="n">
-        <v>7041478</v>
+        <v>7041387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38113-2024 artfynd.xlsx
+++ b/artfynd/A 38113-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120400192</v>
+        <v>120399818</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565904</v>
+        <v>565848</v>
       </c>
       <c r="R2" t="n">
-        <v>7041409</v>
+        <v>7041334</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120400199</v>
+        <v>120399746</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -831,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565908</v>
+        <v>565852</v>
       </c>
       <c r="R3" t="n">
-        <v>7041415</v>
+        <v>7041322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1019,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120399147</v>
+        <v>120398886</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565798</v>
+        <v>565779</v>
       </c>
       <c r="R5" t="n">
-        <v>7041394</v>
+        <v>7041539</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120398741</v>
+        <v>120398916</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1152,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1180,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565735</v>
+        <v>565812</v>
       </c>
       <c r="R6" t="n">
-        <v>7041597</v>
+        <v>7041489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,7 +1256,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120399383</v>
+        <v>120400105</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1287,12 +1291,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1301,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565821</v>
+        <v>565897</v>
       </c>
       <c r="R7" t="n">
-        <v>7041341</v>
+        <v>7041392</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,19 +1360,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398886</v>
+        <v>120400192</v>
       </c>
       <c r="B8" t="n">
         <v>78278</v>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565779</v>
+        <v>565904</v>
       </c>
       <c r="R8" t="n">
-        <v>7041539</v>
+        <v>7041409</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1458,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,19 +1472,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120399818</v>
+        <v>120400312</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1523,21 +1522,16 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565848</v>
+        <v>565899</v>
       </c>
       <c r="R9" t="n">
-        <v>7041334</v>
+        <v>7041429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,22 +1588,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120400275</v>
+        <v>120399383</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,38 +1612,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565901</v>
+        <v>565821</v>
       </c>
       <c r="R10" t="n">
-        <v>7041422</v>
+        <v>7041341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,22 +1709,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120399352</v>
+        <v>120399881</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1733,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565772</v>
+        <v>565862</v>
       </c>
       <c r="R11" t="n">
-        <v>7041373</v>
+        <v>7041347</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,7 +1837,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120400312</v>
+        <v>120399428</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1865,7 +1872,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565899</v>
+        <v>565805</v>
       </c>
       <c r="R12" t="n">
-        <v>7041429</v>
+        <v>7041355</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,19 +1946,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120398926</v>
+        <v>120399679</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1981,12 +1993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1995,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565839</v>
+        <v>565831</v>
       </c>
       <c r="R13" t="n">
-        <v>7041485</v>
+        <v>7041314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,22 +2062,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120399746</v>
+        <v>120400024</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,30 +2086,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2111,13 +2124,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565852</v>
+        <v>565892</v>
       </c>
       <c r="R14" t="n">
-        <v>7041322</v>
+        <v>7041371</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2146,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,7 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,22 +2184,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120399057</v>
+        <v>120398741</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,30 +2208,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2227,10 +2245,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565825</v>
+        <v>565735</v>
       </c>
       <c r="R15" t="n">
-        <v>7041411</v>
+        <v>7041597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,7 +2280,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2290,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,7 +2317,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120400333</v>
+        <v>120399057</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2334,12 +2352,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,10 +2361,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565841</v>
+        <v>565825</v>
       </c>
       <c r="R16" t="n">
-        <v>7041478</v>
+        <v>7041411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2406,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,22 +2421,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120399714</v>
+        <v>120399147</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,47 +2445,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565824</v>
+        <v>565798</v>
       </c>
       <c r="R17" t="n">
-        <v>7041328</v>
+        <v>7041394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2504,7 +2508,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2518,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,19 +2533,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120399580</v>
+        <v>120399994</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2576,7 +2580,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2585,10 +2589,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565788</v>
+        <v>565902</v>
       </c>
       <c r="R18" t="n">
-        <v>7041338</v>
+        <v>7041372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2630,7 +2634,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,10 +2661,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120399968</v>
+        <v>120400275</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2669,42 +2673,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565894</v>
+        <v>565901</v>
       </c>
       <c r="R19" t="n">
-        <v>7041345</v>
+        <v>7041422</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,7 +2773,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120399022</v>
+        <v>120400005</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565878</v>
+        <v>565902</v>
       </c>
       <c r="R20" t="n">
-        <v>7041450</v>
+        <v>7041379</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2894,7 +2894,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120398916</v>
+        <v>120400333</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2929,7 +2929,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2938,10 +2943,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565812</v>
+        <v>565841</v>
       </c>
       <c r="R21" t="n">
-        <v>7041489</v>
+        <v>7041478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,7 +2978,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2983,7 +2988,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2998,19 +3003,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120400005</v>
+        <v>120398926</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3045,12 +3050,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3059,10 +3064,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565902</v>
+        <v>565839</v>
       </c>
       <c r="R22" t="n">
-        <v>7041379</v>
+        <v>7041485</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,7 +3099,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3104,7 +3109,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3131,7 +3136,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120399881</v>
+        <v>120399580</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3175,10 +3180,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565862</v>
+        <v>565788</v>
       </c>
       <c r="R23" t="n">
-        <v>7041347</v>
+        <v>7041338</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3210,7 +3215,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3220,7 +3225,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,7 +3252,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120399614</v>
+        <v>120399714</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3282,7 +3287,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3299,7 +3304,7 @@
         <v>565824</v>
       </c>
       <c r="R24" t="n">
-        <v>7041305</v>
+        <v>7041328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3331,7 +3336,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3341,7 +3346,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3368,7 +3373,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120399679</v>
+        <v>120400132</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3403,7 +3408,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3412,10 +3422,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565831</v>
+        <v>565913</v>
       </c>
       <c r="R25" t="n">
-        <v>7041314</v>
+        <v>7041387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3447,7 +3457,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3467,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3472,22 +3482,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120399994</v>
+        <v>120399352</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3496,42 +3506,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565902</v>
+        <v>565772</v>
       </c>
       <c r="R26" t="n">
-        <v>7041372</v>
+        <v>7041373</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3563,7 +3569,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3573,7 +3579,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3600,7 +3606,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120399428</v>
+        <v>120399968</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3635,12 +3641,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3649,10 +3650,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565805</v>
+        <v>565894</v>
       </c>
       <c r="R27" t="n">
-        <v>7041355</v>
+        <v>7041345</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3684,7 +3685,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3694,7 +3695,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3709,22 +3710,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400024</v>
+        <v>120399022</v>
       </c>
       <c r="B28" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3733,36 +3734,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565892</v>
+        <v>565878</v>
       </c>
       <c r="R28" t="n">
-        <v>7041371</v>
+        <v>7041450</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3843,7 +3843,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400105</v>
+        <v>120400199</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565897</v>
+        <v>565908</v>
       </c>
       <c r="R29" t="n">
-        <v>7041392</v>
+        <v>7041415</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3959,7 +3959,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400132</v>
+        <v>120399614</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565913</v>
+        <v>565824</v>
       </c>
       <c r="R30" t="n">
-        <v>7041387</v>
+        <v>7041305</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38113-2024 artfynd.xlsx
+++ b/artfynd/A 38113-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120399818</v>
+        <v>120399580</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -710,12 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565848</v>
+        <v>565788</v>
       </c>
       <c r="R2" t="n">
-        <v>7041334</v>
+        <v>7041338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,19 +779,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120399746</v>
+        <v>120399428</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -831,7 +826,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565852</v>
+        <v>565805</v>
       </c>
       <c r="R3" t="n">
-        <v>7041322</v>
+        <v>7041355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,19 +900,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120399901</v>
+        <v>120400199</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565882</v>
+        <v>565908</v>
       </c>
       <c r="R4" t="n">
-        <v>7041329</v>
+        <v>7041415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120398886</v>
+        <v>120400333</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,38 +1040,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565779</v>
+        <v>565841</v>
       </c>
       <c r="R5" t="n">
-        <v>7041539</v>
+        <v>7041478</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,19 +1137,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120398916</v>
+        <v>120399714</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1175,7 +1184,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565812</v>
+        <v>565824</v>
       </c>
       <c r="R6" t="n">
-        <v>7041489</v>
+        <v>7041328</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,19 +1258,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120400105</v>
+        <v>120400005</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1291,7 +1305,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565897</v>
+        <v>565902</v>
       </c>
       <c r="R7" t="n">
-        <v>7041392</v>
+        <v>7041379</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120400192</v>
+        <v>120399147</v>
       </c>
       <c r="B8" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565904</v>
+        <v>565798</v>
       </c>
       <c r="R8" t="n">
-        <v>7041409</v>
+        <v>7041394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,19 +1491,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120400312</v>
+        <v>120399057</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1519,7 +1538,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1528,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565899</v>
+        <v>565825</v>
       </c>
       <c r="R9" t="n">
-        <v>7041429</v>
+        <v>7041411</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1619,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120399383</v>
+        <v>120398926</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1640,7 +1659,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565821</v>
+        <v>565839</v>
       </c>
       <c r="R10" t="n">
-        <v>7041341</v>
+        <v>7041485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1713,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,7 +1740,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120399881</v>
+        <v>120399994</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1756,7 +1775,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1765,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565862</v>
+        <v>565902</v>
       </c>
       <c r="R11" t="n">
-        <v>7041347</v>
+        <v>7041372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1829,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,7 +1856,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120399428</v>
+        <v>120400312</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1872,12 +1891,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1886,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565805</v>
+        <v>565899</v>
       </c>
       <c r="R12" t="n">
-        <v>7041355</v>
+        <v>7041429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1935,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1945,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,22 +1960,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120399679</v>
+        <v>120400192</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,42 +1984,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565831</v>
+        <v>565904</v>
       </c>
       <c r="R13" t="n">
-        <v>7041314</v>
+        <v>7041409</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,22 +2072,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400024</v>
+        <v>120400105</v>
       </c>
       <c r="B14" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,36 +2096,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2124,13 +2128,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565892</v>
+        <v>565897</v>
       </c>
       <c r="R14" t="n">
-        <v>7041371</v>
+        <v>7041392</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2159,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2173,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,22 +2188,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398741</v>
+        <v>120399614</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,35 +2212,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2245,10 +2249,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565735</v>
+        <v>565824</v>
       </c>
       <c r="R15" t="n">
-        <v>7041597</v>
+        <v>7041305</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2290,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,19 +2309,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120399057</v>
+        <v>120399901</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2352,7 +2356,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2361,10 +2365,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565825</v>
+        <v>565882</v>
       </c>
       <c r="R16" t="n">
-        <v>7041411</v>
+        <v>7041329</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2400,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,7 +2410,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,7 +2437,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120399147</v>
+        <v>120400275</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2473,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565798</v>
+        <v>565901</v>
       </c>
       <c r="R17" t="n">
-        <v>7041394</v>
+        <v>7041422</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,7 +2512,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2518,7 +2522,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,10 +2549,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120399994</v>
+        <v>120399352</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2557,42 +2561,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565902</v>
+        <v>565772</v>
       </c>
       <c r="R18" t="n">
-        <v>7041372</v>
+        <v>7041373</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,10 +2661,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400275</v>
+        <v>120399679</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,38 +2673,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565901</v>
+        <v>565831</v>
       </c>
       <c r="R19" t="n">
-        <v>7041422</v>
+        <v>7041314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2736,7 +2740,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2746,7 +2750,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,10 +2777,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120400005</v>
+        <v>120398886</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2785,47 +2789,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565902</v>
+        <v>565779</v>
       </c>
       <c r="R20" t="n">
-        <v>7041379</v>
+        <v>7041539</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,7 +2852,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2867,7 +2862,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,22 +2877,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120400333</v>
+        <v>120400024</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2906,35 +2901,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2943,13 +2939,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565841</v>
+        <v>565892</v>
       </c>
       <c r="R21" t="n">
-        <v>7041478</v>
+        <v>7041371</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2978,7 +2974,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2988,7 +2984,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3015,7 +3011,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120398926</v>
+        <v>120399746</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3050,12 +3046,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3064,10 +3055,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565839</v>
+        <v>565852</v>
       </c>
       <c r="R22" t="n">
-        <v>7041485</v>
+        <v>7041322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3099,7 +3090,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3109,7 +3100,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3124,19 +3115,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120399580</v>
+        <v>120399968</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3180,10 +3171,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565788</v>
+        <v>565894</v>
       </c>
       <c r="R23" t="n">
-        <v>7041338</v>
+        <v>7041345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3215,7 +3206,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3225,7 +3216,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3252,7 +3243,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120399714</v>
+        <v>120398916</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3287,12 +3278,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3301,10 +3287,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565824</v>
+        <v>565812</v>
       </c>
       <c r="R24" t="n">
-        <v>7041328</v>
+        <v>7041489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3336,7 +3322,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3346,7 +3332,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3361,19 +3347,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400132</v>
+        <v>120399383</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3408,7 +3394,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3422,10 +3408,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565913</v>
+        <v>565821</v>
       </c>
       <c r="R25" t="n">
-        <v>7041387</v>
+        <v>7041341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3457,7 +3443,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3467,7 +3453,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3494,10 +3480,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120399352</v>
+        <v>120398741</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3510,34 +3496,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565772</v>
+        <v>565735</v>
       </c>
       <c r="R26" t="n">
-        <v>7041373</v>
+        <v>7041597</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3569,7 +3564,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3579,7 +3574,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,7 +3601,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120399968</v>
+        <v>120399881</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3650,10 +3645,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565894</v>
+        <v>565862</v>
       </c>
       <c r="R27" t="n">
-        <v>7041345</v>
+        <v>7041347</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3685,7 +3680,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3695,7 +3690,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3722,7 +3717,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120399022</v>
+        <v>120400132</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3757,7 +3752,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3771,10 +3766,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565878</v>
+        <v>565913</v>
       </c>
       <c r="R28" t="n">
-        <v>7041450</v>
+        <v>7041387</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3806,7 +3801,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3816,7 +3811,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3843,7 +3838,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400199</v>
+        <v>120399818</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3878,7 +3873,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565908</v>
+        <v>565848</v>
       </c>
       <c r="R29" t="n">
-        <v>7041415</v>
+        <v>7041334</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3947,19 +3947,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120399614</v>
+        <v>120399022</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565824</v>
+        <v>565878</v>
       </c>
       <c r="R30" t="n">
-        <v>7041305</v>
+        <v>7041450</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 38113-2024 artfynd.xlsx
+++ b/artfynd/A 38113-2024 artfynd.xlsx
@@ -3601,7 +3601,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120399881</v>
+        <v>120400132</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3639,16 +3639,21 @@
           <t>10</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565862</v>
+        <v>565913</v>
       </c>
       <c r="R27" t="n">
-        <v>7041347</v>
+        <v>7041387</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3680,7 +3685,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3690,7 +3695,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3705,19 +3710,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400132</v>
+        <v>120399881</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3755,21 +3760,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565913</v>
+        <v>565862</v>
       </c>
       <c r="R28" t="n">
-        <v>7041387</v>
+        <v>7041347</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,12 +3826,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 38113-2024 artfynd.xlsx
+++ b/artfynd/A 38113-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120399580</v>
+        <v>120399968</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565788</v>
+        <v>565894</v>
       </c>
       <c r="R2" t="n">
-        <v>7041338</v>
+        <v>7041345</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1028,7 +1028,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120400333</v>
+        <v>120400132</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565841</v>
+        <v>565913</v>
       </c>
       <c r="R5" t="n">
-        <v>7041478</v>
+        <v>7041387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120399714</v>
+        <v>120399614</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1201,7 +1201,7 @@
         <v>565824</v>
       </c>
       <c r="R6" t="n">
-        <v>7041328</v>
+        <v>7041305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120400005</v>
+        <v>120400275</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,47 +1282,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565902</v>
+        <v>565901</v>
       </c>
       <c r="R7" t="n">
-        <v>7041379</v>
+        <v>7041422</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,22 +1370,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120399147</v>
+        <v>120399994</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,38 +1394,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565798</v>
+        <v>565902</v>
       </c>
       <c r="R8" t="n">
-        <v>7041394</v>
+        <v>7041372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120399057</v>
+        <v>120400024</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,30 +1510,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1547,13 +1548,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565825</v>
+        <v>565892</v>
       </c>
       <c r="R9" t="n">
-        <v>7041411</v>
+        <v>7041371</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,19 +1608,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120398926</v>
+        <v>120399818</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1654,12 +1655,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1668,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565839</v>
+        <v>565848</v>
       </c>
       <c r="R10" t="n">
-        <v>7041485</v>
+        <v>7041334</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120399994</v>
+        <v>120398886</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,42 +1753,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565902</v>
+        <v>565779</v>
       </c>
       <c r="R11" t="n">
-        <v>7041372</v>
+        <v>7041539</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1819,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1829,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400192</v>
+        <v>120400333</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,38 +1981,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565904</v>
+        <v>565841</v>
       </c>
       <c r="R13" t="n">
-        <v>7041409</v>
+        <v>7041478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2063,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,7 +2090,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400105</v>
+        <v>120399746</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2119,7 +2125,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2128,10 +2134,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565897</v>
+        <v>565852</v>
       </c>
       <c r="R14" t="n">
-        <v>7041392</v>
+        <v>7041322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,7 +2169,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2173,7 +2179,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,7 +2206,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120399614</v>
+        <v>120398926</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2235,12 +2241,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2249,10 +2255,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565824</v>
+        <v>565839</v>
       </c>
       <c r="R15" t="n">
-        <v>7041305</v>
+        <v>7041485</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2290,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2300,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2321,7 +2327,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120399901</v>
+        <v>120399679</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2356,7 +2362,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2365,10 +2371,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565882</v>
+        <v>565831</v>
       </c>
       <c r="R16" t="n">
-        <v>7041329</v>
+        <v>7041314</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,7 +2406,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2416,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,10 +2443,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400275</v>
+        <v>120400005</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,38 +2455,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565901</v>
+        <v>565902</v>
       </c>
       <c r="R17" t="n">
-        <v>7041422</v>
+        <v>7041379</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2512,7 +2527,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2522,7 +2537,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,22 +2552,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120399352</v>
+        <v>120400105</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2561,38 +2576,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565772</v>
+        <v>565897</v>
       </c>
       <c r="R18" t="n">
-        <v>7041373</v>
+        <v>7041392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2624,7 +2643,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2634,7 +2653,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120399679</v>
+        <v>120400192</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,42 +2692,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565831</v>
+        <v>565904</v>
       </c>
       <c r="R19" t="n">
-        <v>7041314</v>
+        <v>7041409</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2740,7 +2755,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2750,7 +2765,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,22 +2780,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120398886</v>
+        <v>120399352</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2793,21 +2808,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2817,10 +2832,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565779</v>
+        <v>565772</v>
       </c>
       <c r="R20" t="n">
-        <v>7041539</v>
+        <v>7041373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2852,7 +2867,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2862,7 +2877,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,10 +2904,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120400024</v>
+        <v>120399383</v>
       </c>
       <c r="B21" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2901,36 +2916,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2939,13 +2953,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565892</v>
+        <v>565821</v>
       </c>
       <c r="R21" t="n">
-        <v>7041371</v>
+        <v>7041341</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2974,7 +2988,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2984,7 +2998,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,7 +3025,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120399746</v>
+        <v>120399714</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3049,16 +3063,21 @@
           <t>5</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565852</v>
+        <v>565824</v>
       </c>
       <c r="R22" t="n">
-        <v>7041322</v>
+        <v>7041328</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,7 +3109,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3100,7 +3119,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,22 +3134,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120399968</v>
+        <v>120399147</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3139,42 +3158,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565894</v>
+        <v>565798</v>
       </c>
       <c r="R23" t="n">
-        <v>7041345</v>
+        <v>7041394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3206,7 +3221,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3216,7 +3231,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,7 +3258,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120398916</v>
+        <v>120399057</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3287,10 +3302,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565812</v>
+        <v>565825</v>
       </c>
       <c r="R24" t="n">
-        <v>7041489</v>
+        <v>7041411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3322,7 +3337,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3332,7 +3347,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,7 +3374,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120399383</v>
+        <v>120398916</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3394,12 +3409,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3408,10 +3418,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565821</v>
+        <v>565812</v>
       </c>
       <c r="R25" t="n">
-        <v>7041341</v>
+        <v>7041489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3443,7 +3453,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3453,7 +3463,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3468,22 +3478,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120398741</v>
+        <v>120399022</v>
       </c>
       <c r="B26" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3492,35 +3502,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3529,10 +3539,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565735</v>
+        <v>565878</v>
       </c>
       <c r="R26" t="n">
-        <v>7041597</v>
+        <v>7041450</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3564,7 +3574,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3574,7 +3584,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3589,19 +3599,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120400132</v>
+        <v>120399580</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3639,21 +3649,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565913</v>
+        <v>565788</v>
       </c>
       <c r="R27" t="n">
-        <v>7041387</v>
+        <v>7041338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3685,7 +3690,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3695,7 +3700,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3710,22 +3715,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120399881</v>
+        <v>120398741</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3734,30 +3739,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3766,10 +3776,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565862</v>
+        <v>565735</v>
       </c>
       <c r="R28" t="n">
-        <v>7041347</v>
+        <v>7041597</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3801,7 +3811,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3811,7 +3821,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3838,7 +3848,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120399818</v>
+        <v>120399881</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3873,12 +3883,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3887,10 +3892,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565848</v>
+        <v>565862</v>
       </c>
       <c r="R29" t="n">
-        <v>7041334</v>
+        <v>7041347</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3922,7 +3927,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3932,7 +3937,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3947,19 +3952,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120399022</v>
+        <v>120399901</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3994,12 +3999,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565878</v>
+        <v>565882</v>
       </c>
       <c r="R30" t="n">
-        <v>7041450</v>
+        <v>7041329</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4068,12 +4068,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 38113-2024 artfynd.xlsx
+++ b/artfynd/A 38113-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120399968</v>
+        <v>120399022</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -710,7 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565894</v>
+        <v>565878</v>
       </c>
       <c r="R2" t="n">
-        <v>7041345</v>
+        <v>7041450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +784,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120399428</v>
+        <v>120398916</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -826,12 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565805</v>
+        <v>565812</v>
       </c>
       <c r="R3" t="n">
-        <v>7041355</v>
+        <v>7041489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,19 +900,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120400199</v>
+        <v>120400105</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565908</v>
+        <v>565897</v>
       </c>
       <c r="R4" t="n">
-        <v>7041415</v>
+        <v>7041392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,7 +1028,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120400132</v>
+        <v>120399614</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565913</v>
+        <v>565824</v>
       </c>
       <c r="R5" t="n">
-        <v>7041387</v>
+        <v>7041305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120399614</v>
+        <v>120400024</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,35 +1161,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1198,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565824</v>
+        <v>565892</v>
       </c>
       <c r="R6" t="n">
-        <v>7041305</v>
+        <v>7041371</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120400275</v>
+        <v>120400312</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,38 +1283,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565901</v>
+        <v>565899</v>
       </c>
       <c r="R7" t="n">
-        <v>7041422</v>
+        <v>7041429</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120399994</v>
+        <v>120399428</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1417,7 +1422,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565902</v>
+        <v>565805</v>
       </c>
       <c r="R8" t="n">
-        <v>7041372</v>
+        <v>7041355</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1496,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120400024</v>
+        <v>120399994</v>
       </c>
       <c r="B9" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,36 +1520,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,13 +1552,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565892</v>
+        <v>565902</v>
       </c>
       <c r="R9" t="n">
-        <v>7041371</v>
+        <v>7041372</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,19 +1612,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120399818</v>
+        <v>120400333</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1655,7 +1659,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1669,10 +1673,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565848</v>
+        <v>565841</v>
       </c>
       <c r="R10" t="n">
-        <v>7041334</v>
+        <v>7041478</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120398886</v>
+        <v>120400192</v>
       </c>
       <c r="B11" t="n">
         <v>78278</v>
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565779</v>
+        <v>565904</v>
       </c>
       <c r="R11" t="n">
-        <v>7041539</v>
+        <v>7041409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,19 +1845,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120400312</v>
+        <v>120399714</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1888,7 +1892,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1897,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565899</v>
+        <v>565824</v>
       </c>
       <c r="R12" t="n">
-        <v>7041429</v>
+        <v>7041328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,7 +1951,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,19 +1966,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400333</v>
+        <v>120398926</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -2004,12 +2013,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2018,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565841</v>
+        <v>565839</v>
       </c>
       <c r="R13" t="n">
-        <v>7041478</v>
+        <v>7041485</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2062,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,7 +2072,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120399746</v>
+        <v>120399352</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,42 +2111,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565852</v>
+        <v>565772</v>
       </c>
       <c r="R14" t="n">
-        <v>7041322</v>
+        <v>7041373</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2179,7 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,7 +2211,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120398926</v>
+        <v>120399057</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2241,12 +2246,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565839</v>
+        <v>565825</v>
       </c>
       <c r="R15" t="n">
-        <v>7041485</v>
+        <v>7041411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2315,19 +2315,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120399679</v>
+        <v>120400005</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2362,7 +2362,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2371,10 +2376,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565831</v>
+        <v>565902</v>
       </c>
       <c r="R16" t="n">
-        <v>7041314</v>
+        <v>7041379</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,7 +2411,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2416,7 +2421,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,19 +2436,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400005</v>
+        <v>120400199</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2478,12 +2483,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565902</v>
+        <v>565908</v>
       </c>
       <c r="R17" t="n">
-        <v>7041379</v>
+        <v>7041415</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,19 +2552,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120400105</v>
+        <v>120399679</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565897</v>
+        <v>565831</v>
       </c>
       <c r="R18" t="n">
-        <v>7041392</v>
+        <v>7041314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400192</v>
+        <v>120398886</v>
       </c>
       <c r="B19" t="n">
         <v>78278</v>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565904</v>
+        <v>565779</v>
       </c>
       <c r="R19" t="n">
-        <v>7041409</v>
+        <v>7041539</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,22 +2780,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120399352</v>
+        <v>120399383</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,38 +2804,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565772</v>
+        <v>565821</v>
       </c>
       <c r="R20" t="n">
-        <v>7041373</v>
+        <v>7041341</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2867,7 +2876,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2877,7 +2886,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,19 +2901,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120399383</v>
+        <v>120399881</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2939,12 +2948,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2953,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565821</v>
+        <v>565862</v>
       </c>
       <c r="R21" t="n">
-        <v>7041341</v>
+        <v>7041347</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,7 +2992,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2998,7 +3002,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,19 +3017,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120399714</v>
+        <v>120399901</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3060,12 +3064,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3074,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565824</v>
+        <v>565882</v>
       </c>
       <c r="R22" t="n">
-        <v>7041328</v>
+        <v>7041329</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3109,7 +3108,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3119,7 +3118,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3134,22 +3133,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120399147</v>
+        <v>120398741</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3162,34 +3161,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565798</v>
+        <v>565735</v>
       </c>
       <c r="R23" t="n">
-        <v>7041394</v>
+        <v>7041597</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3221,7 +3229,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3231,7 +3239,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3258,10 +3266,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120399057</v>
+        <v>120400275</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3270,42 +3278,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565825</v>
+        <v>565901</v>
       </c>
       <c r="R24" t="n">
-        <v>7041411</v>
+        <v>7041422</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3337,7 +3341,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3347,7 +3351,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3374,7 +3378,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120398916</v>
+        <v>120400132</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3412,16 +3416,21 @@
           <t>10</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565812</v>
+        <v>565913</v>
       </c>
       <c r="R25" t="n">
-        <v>7041489</v>
+        <v>7041387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3453,7 +3462,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3463,7 +3472,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3478,19 +3487,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120399022</v>
+        <v>120399746</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3525,12 +3534,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3539,10 +3543,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565878</v>
+        <v>565852</v>
       </c>
       <c r="R26" t="n">
-        <v>7041450</v>
+        <v>7041322</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3574,7 +3578,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3584,7 +3588,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,12 +3603,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3727,10 +3731,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120398741</v>
+        <v>120399147</v>
       </c>
       <c r="B28" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3743,43 +3747,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565735</v>
+        <v>565798</v>
       </c>
       <c r="R28" t="n">
-        <v>7041597</v>
+        <v>7041394</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3811,7 +3806,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3821,7 +3816,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3848,7 +3843,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120399881</v>
+        <v>120399968</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3892,10 +3887,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565862</v>
+        <v>565894</v>
       </c>
       <c r="R29" t="n">
-        <v>7041347</v>
+        <v>7041345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3927,7 +3922,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3937,7 +3932,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3964,7 +3959,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120399901</v>
+        <v>120399818</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3999,7 +3994,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565882</v>
+        <v>565848</v>
       </c>
       <c r="R30" t="n">
-        <v>7041329</v>
+        <v>7041334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4068,12 +4068,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 38113-2024 artfynd.xlsx
+++ b/artfynd/A 38113-2024 artfynd.xlsx
@@ -3378,7 +3378,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400132</v>
+        <v>120399746</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3413,12 +3413,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3427,10 +3422,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565913</v>
+        <v>565852</v>
       </c>
       <c r="R25" t="n">
-        <v>7041387</v>
+        <v>7041322</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3462,7 +3457,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3472,7 +3467,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3487,19 +3482,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120399746</v>
+        <v>120400132</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3534,7 +3529,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565852</v>
+        <v>565913</v>
       </c>
       <c r="R26" t="n">
-        <v>7041322</v>
+        <v>7041387</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3603,12 +3603,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
